--- a/reports/셀린느/history/2026-05-07/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/history/2026-05-07/셀린느_league_mgf_report.xlsx
@@ -80,522 +80,525 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>6경 6578조 3092억 4574만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.05.07</t>
+  </si>
+  <si>
+    <t>리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>4경 8849조 8735억 7125만</t>
+  </si>
+  <si>
+    <t>길마 : 예습2, 부길마 : 단우성, 갓짭</t>
+  </si>
+  <si>
+    <t>예습2</t>
+  </si>
+  <si>
+    <t>더샾</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8D%94%EC%83%BE</t>
+  </si>
+  <si>
+    <t>Scania 26</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>4경 6244조 9438억 8228만</t>
+  </si>
+  <si>
+    <t>해시태그 샾 닉변 디코 톡방 친화력 필수요</t>
+  </si>
+  <si>
+    <t>샾로로</t>
+  </si>
+  <si>
+    <t>RAINBOW</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>5경 511조 2265억 3073만</t>
+  </si>
+  <si>
+    <t>가입문의: 화질, 한딸기, 람볼기니 토벌100등 안쪽 귓 주세요. 길컨 , 파퀘, 자쿰, 혼테일 모든 컨테츠 활발하게 즐길 사람!!</t>
+  </si>
+  <si>
+    <t>화질</t>
+  </si>
+  <si>
+    <t>샴페인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%83%B4%ED%8E%98%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>Scania 43</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>4경 662조 1265억 9271만</t>
+  </si>
+  <si>
+    <t>Scania43 NO.1 Champagne 가입문의 : 나인티,돌진상,미르몽</t>
+  </si>
+  <si>
+    <t>나인티</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>3경 27조 8635억 7445만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 904조 1185억 7211만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6493조 5045억 7772만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>5860조 1812억 2503만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>3106조 9258억 9914만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>2011조 4544억 3476만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1042조 3116억 6204만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1007조 3178억 5658만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>874조 5211억 9379만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>869조 5677억 141만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>684조 4401억 9646만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>481조 5847억 7403만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>닼나짱2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>379조 5440억 9162만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>366조 6787억 5438만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>334조 4614억 9803만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>뽀삐스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>275조 8357억 446만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>273조 8981억 703만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>266조 8078억 6673만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>254조 2629억 9000만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>239조 5598억 9073만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>186조 7933억 7887만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>143조 3408억 6701만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>92조 4870억 8016만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>70조 9879억 8078만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>70조 9613억 4646만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>59조 7773억 9141만</t>
+  </si>
+  <si>
     <t>27</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>6경 6578조 3092억 4574만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.05.07</t>
-  </si>
-  <si>
-    <t>리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>4경 8825조 3616억 7794만</t>
-  </si>
-  <si>
-    <t>길마 : 예습2, 부길마 : 단우성, 갓짭</t>
-  </si>
-  <si>
-    <t>예습2</t>
-  </si>
-  <si>
-    <t>더샾</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8D%94%EC%83%BE</t>
-  </si>
-  <si>
-    <t>Scania 26</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>26명</t>
-  </si>
-  <si>
-    <t>4경 6221조 1818억 5532만</t>
-  </si>
-  <si>
-    <t>해시태그 샾 닉변 디코 톡방 친화력 필수요</t>
-  </si>
-  <si>
-    <t>샾로로</t>
-  </si>
-  <si>
-    <t>RAINBOW</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>5경 511조 2265억 3073만</t>
-  </si>
-  <si>
-    <t>가입문의: 화질, 한딸기, 람볼기니 토벌100등 안쪽 귓 주세요. 길컨 , 파퀘, 자쿰, 혼테일 모든 컨테츠 활발하게 즐길 사람!!</t>
-  </si>
-  <si>
-    <t>화질</t>
-  </si>
-  <si>
-    <t>샴페인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%83%B4%ED%8E%98%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>Scania 43</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>4경 662조 1265억 9271만</t>
-  </si>
-  <si>
-    <t>Scania43 NO.1 Champagne 가입문의 : 나인티,돌진상,미르몽</t>
-  </si>
-  <si>
-    <t>나인티</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>3경 27조 8635억 7445만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 904조 1185억 7211만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6493조 5045억 7772만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>5860조 1812억 2503만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>3106조 9258억 9914만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>2011조 4544억 3476만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1042조 3116억 6204만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1007조 3178억 5658만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>874조 5211억 9379만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>869조 5677억 141만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>684조 4401억 9646만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>481조 5847억 7403만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>닼나짱2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%A7%B12</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>379조 5440억 9162만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>366조 6787억 5438만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>334조 4614억 9803만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>뽀삐스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%82%90%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>275조 8357억 446만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>273조 8981억 703만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>266조 8078억 6673만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>254조 2629억 9000만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>239조 5598억 9073만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>186조 7933억 7887만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>143조 3408억 6701만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>92조 4870억 8016만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>70조 9879억 8078만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>70조 9613억 4646만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>59조 7773억 9141만</t>
-  </si>
-  <si>
     <t>김치싸대기</t>
   </si>
   <si>
@@ -608,9 +611,6 @@
     <t>55조 7049억 3694만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>3139조 9177억 3699만</t>
+    <t>3155조 1786억 3847만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -707,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>2233조 8297억 501만</t>
+    <t>2234조 6080억 6842만</t>
   </si>
   <si>
     <t>박카쓰</t>
@@ -743,7 +743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>387조 7083억 9727만</t>
+    <t>387조 8160억 8513만</t>
   </si>
   <si>
     <t>단우성</t>
@@ -797,7 +797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
   </si>
   <si>
-    <t>101조 2205억 1763만</t>
+    <t>108조 3197억 7591만</t>
   </si>
   <si>
     <t>charon</t>
@@ -833,7 +833,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%81%EB%AF%BC</t>
   </si>
   <si>
-    <t>65조 6040억 5756만</t>
+    <t>66조 8478억 6596만</t>
   </si>
   <si>
     <t>히째히째</t>
@@ -845,7 +845,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>49조 3135억 6616만</t>
+    <t>49조 3354억 4002만</t>
   </si>
   <si>
     <t>뜨람프</t>
@@ -1010,7 +1010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EB%9E%80</t>
   </si>
   <si>
-    <t>476조 9811억 9380만</t>
+    <t>477조 993억 7676만</t>
   </si>
   <si>
     <t>샾76세현수</t>
@@ -1532,6 +1532,18 @@
     <t>9조 1050억 7348만</t>
   </si>
   <si>
+    <t>릴라주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B4%EB%9D%BC%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>3조 5536억 7982만</t>
+  </si>
+  <si>
     <t>군평천</t>
   </si>
   <si>
@@ -1542,18 +1554,6 @@
   </si>
   <si>
     <t>3조 4943억 51만</t>
-  </si>
-  <si>
-    <t>릴라주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B4%EB%9D%BC%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>3조 4465억 9921만</t>
   </si>
   <si>
     <t>니어멍뼛가루</t>
@@ -3192,16 +3192,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
@@ -3210,10 +3210,10 @@
         <v>99</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3224,7 +3224,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>194</v>
@@ -3935,7 +3935,7 @@
         <v>99</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>256</v>
@@ -4031,7 +4031,7 @@
         <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>265</v>
@@ -4063,7 +4063,7 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>268</v>
@@ -4095,7 +4095,7 @@
         <v>271</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>272</v>
@@ -4127,7 +4127,7 @@
         <v>72</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>275</v>
@@ -4223,7 +4223,7 @@
         <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>284</v>
@@ -4237,7 +4237,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>285</v>
@@ -4269,7 +4269,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>288</v>
@@ -5074,7 +5074,7 @@
         <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>356</v>
@@ -5762,7 +5762,7 @@
         <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>418</v>
@@ -5826,7 +5826,7 @@
         <v>149</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>424</v>
@@ -5890,7 +5890,7 @@
         <v>149</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>430</v>
@@ -5954,7 +5954,7 @@
         <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>435</v>
@@ -6018,7 +6018,7 @@
         <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>441</v>
@@ -6096,7 +6096,7 @@
         <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>448</v>
@@ -6128,7 +6128,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>451</v>
@@ -6486,7 +6486,7 @@
         <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>477</v>
@@ -6902,7 +6902,7 @@
         <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>518</v>
@@ -6934,7 +6934,7 @@
         <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>521</v>
@@ -7108,7 +7108,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>538</v>
@@ -7140,7 +7140,7 @@
         <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>541</v>
